--- a/products.xlsx
+++ b/products.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\Amazon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24DB082-9B32-4D9E-92E6-346E9ABB0DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193F5692-5344-4438-BDBB-06BE0FA03AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
   <si>
     <t>name</t>
   </si>
@@ -34,243 +34,9 @@
     <t>category</t>
   </si>
   <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_744049-MLA99539379058_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Liquidificador Turbo Power Mondial 550W - L-99 FB</t>
-  </si>
-  <si>
-    <t>Electrolux Efficient Esi10 a vapor e ferro seco, cor azul</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_875816-MLA99972137443_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Eletrodoméstico</t>
-  </si>
-  <si>
-    <t>Fritadeira Elétrica AFON-12L-BG Forno Oven 12 Litros Preto Mondial</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_720182-MLA100247452907_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Ventilador De Coluna Turbo 40cm Bronze Ventisol</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_953439-MLA99450372734_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Headset Qcy H3 Anc Adaptativo Bluetooth 5.3 Multiponto 60h Cor Preto</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_902982-MLA88535253704_072025-F.webp</t>
-  </si>
-  <si>
-    <t>Parafusadeira Furadeira De Impacto The Black Tools Profissional TB-21PX 2 Baterias Com Maleta 60Hz Amarelo</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_865332-MLA96868279679_102025-F.webp</t>
-  </si>
-  <si>
-    <t>Ferramentas</t>
-  </si>
-  <si>
-    <t>Climatizador Ar Frio Portátil Evaporativo 16 Litros Umidificador Ventisol Clin 16</t>
-  </si>
-  <si>
-    <t>Climatizador</t>
-  </si>
-  <si>
-    <t>Xícara Copo Café Térmico Inox 80ml Expresso Parede Dupla</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_801309-MLB89093855460_082025-F-xicara-copo-cafe-termico-inox-80ml-expresso-parede-dupla.webp</t>
-  </si>
-  <si>
-    <t>Canecas e copos térmicos</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_843341-MLA99946710327_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Iluminação</t>
-  </si>
-  <si>
-    <t>Ventilador De Mesa Mondial Super Power 6 Pás 30cm Preto Azul Vsp-30-ap</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_860437-MLA99700923002_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Ventilador</t>
-  </si>
-  <si>
-    <t>Climatizador De Ar Wap Air Fresh 4 Em 1 Silencioso Com Reser</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_921663-MLA98636631691_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Mini Compressor Digital Simake Bomba De Encher Pneus Portátil Para Carro Bicicleta Motocicletas Cor Preto Com Calibrador</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_900674-MLA100087555981_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Esporte</t>
-  </si>
-  <si>
-    <t>Projetor Smart Portátil Several Importados Full Hd 4k Android 11 Wi-fi Bluetooth Mini Projetor Home Theater Cinema Em Casa Cor Branco Imagem Nítida Som Potente Compatível Com Diversos Dispositivos</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_752031-MLA97933964606_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Projetores</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_709939-MLB89343355425_082025-F-kit-5-arandela-meia-lua-led-8w-8-fachos-ip66-bivolt-3000k.webp</t>
-  </si>
-  <si>
-    <t>Kit 5 Arandela Meia Lua Led 8w 8 Fachos Ip66 Bivolt 3000k</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_860270-MLB82943676385_032025-F.webp</t>
-  </si>
-  <si>
-    <t>Kit 2 Lâmpada Mata Mosquito Led Uv Pernilongo Frete Gratis 127/220v</t>
-  </si>
-  <si>
-    <t>Torneira Elétrica Digital Aço Escovado Cozinha Banheiro Aquecedor 3000w</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_695329-MLA99450348258_112025-F.webp</t>
-  </si>
-  <si>
     <t>Casa</t>
   </si>
   <si>
-    <t>Mesa De Som 4 Canais 2 Microfones Home Mixer Bluetooth Usb</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_867413-MLA99992012721_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Lazer</t>
-  </si>
-  <si>
-    <t>Power Bank 20.000mah Haixia Carregador Rápido Com Display Portátil Branco</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_992444-MLA99468808790_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Eletronico</t>
-  </si>
-  <si>
-    <t>800mlgarrafa Térmica Água Squeeze Inox Academiaquente E Frio</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_795242-MLB97132720589_112025-F-800mlgarrafa-termica-agua-squeeze-inox-academiaquente-e-frio.webp</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_790464-MLB103906889650_012026-F-copo-taca-2-em-1-termica-cocktail-glass-414ml-em-aco-inox.webp</t>
-  </si>
-  <si>
-    <t>Copo Taça 2 Em 1 Térmica Cocktail Glass 414ml Em Aço Inox</t>
-  </si>
-  <si>
-    <t>Limpa Ar Condicionado Spray Orbi-air Carro Higienização</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_900675-MLB90291373988_082025-F-limpa-ar-condicionado-spray-orbi-air-carro-higienizaco.webp</t>
-  </si>
-  <si>
-    <t>Automoveis</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_875537-MLA99498937668_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Barbeador E Cortador De Cabelo 3 Em 1 Kemei Km-6558</t>
-  </si>
-  <si>
-    <t>Saúde / Beleza</t>
-  </si>
-  <si>
-    <t>Escova de Dente Elétrica Oral-B Power Pro Precision Clean 1 Unidade</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_868166-MLA90028576901_082025-F.webp</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_719702-MLB101390943178_122025-F-kit-conserto-remendo-furo-pneu-carro-moto-ferramenta-reparo.webp</t>
-  </si>
-  <si>
-    <t>Kit Conserto Remendo Furo Pneu Carro Moto Ferramenta Reparo</t>
-  </si>
-  <si>
-    <t>Picador Cortador De Legumes Médio Batata Tomate Frutas</t>
-  </si>
-  <si>
-    <t>Headsets</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_876544-MLA99513954036_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Purificador De Água Natural - Vivax Ibbl Cor Branco</t>
-  </si>
-  <si>
-    <t>Purificador De Água Ibbl Vivax Cinza Certificado Inmetro</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_993004-MLA99910338111_112025-F.webp</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_979721-MLA79634440558_102024-F.webp</t>
-  </si>
-  <si>
-    <t>Carregador Inteligente De Bateria Automotiva Carro Moto Caminhão Jet Sky Empilhadeira 12v 6 Amperes Bivolt 110/220 V - Thop Tech</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_941221-MLA99362401578_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Kit De Internet Via Satelite Starlink Mini Branco</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_799612-MLA95359719699_102025-F.webp</t>
-  </si>
-  <si>
-    <t>Creatina Monohidratada 1Kg Soldiers Nutrition 100% Pura Importada Alta Performance Músculo Treino</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_736821-MLA99962382095_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Chuveiro Lorenzetti Loren Shower Eletrônico Branco 6800W</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_896908-MLA101388142032_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Registro Regulador Gás Cozinha Botijão Domestico Com Visor</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_689702-MLB99978635776_122025-F.webp</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_671434-MLA99990718455_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Solução Nutritiva Hidroponia 1000L Plantpar Linha Flex Azul Vermelho</t>
-  </si>
-  <si>
-    <t>Jardim</t>
-  </si>
-  <si>
     <t>Ver produtos Internacional</t>
   </si>
   <si>
@@ -280,581 +46,164 @@
     <t>50 Unidades De Copos De Rede De Plástico, Malha Com Fenda</t>
   </si>
   <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_738534-MLB99276147747_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Espanta Mosca Ventilador Repelente De Mosquito Para Mesa</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_839239-MLA99452130470_112025-F.webp</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_654561-MLU74941455480_032024-F.webp</t>
-  </si>
-  <si>
-    <t>Panquequeira E Crepioca Elétrica 3 Em 1 900w Britânia</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_844986-MLB90069025741_082025-F-maquina-de-crepe-crepeira-crepera-hotdog-linguica-queijo-110.webp</t>
-  </si>
-  <si>
-    <t>Maquina De Crepe Crepeira Crepera Hotdog Linguiça Queijo 110</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_701271-MLA104689874488_012026-F.webp</t>
-  </si>
-  <si>
-    <t>Kit 2câmera Ip Icsee Prova D'água Infravermelho Externa Wifi - HW</t>
-  </si>
-  <si>
-    <t>Kit Caneta Fine Line Cores Ponta Fina 0.4mm Cor Da Ti Tinta Kit 24 cores CORPO COLORIDO</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_Q_NP_890345-MLU77685731002_072024-R.webp</t>
-  </si>
-  <si>
-    <t>Volta as aulas</t>
-  </si>
-  <si>
-    <t>Lápis de Cor Multicolor 24 Cores 2B Para Desenho Modelo 11.2400N</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_707789-MLU72753307656_112023-F.webp</t>
-  </si>
-  <si>
-    <t>Papel A4 Sulfite Cor Branco 75g 500 Folhas Premium Resma</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_613006-MLA101345266963_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Resistência Lorenzetti Acqua Ultra 220v 7800w Ref 3065b</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_808826-MLB79017709196_092024-F.webp</t>
-  </si>
-  <si>
-    <t>Fio Nylon Aço 3mm Branco 35m Cinza Roçadeira Stihl Kawashima</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_636648-MLA99999816073_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Raquete Beach Tennis Carbono Camewin Cores Modelos + Estojo Cor Verde</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_986008-MLA99979982031_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Raquete Beach Tennis Shark Tour Modelo 2022</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_860626-MLA99986882345_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Conjunto Top Shorts Feminino Los Angeles Slim Moda Academia</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_982273-MLB79171128329_092024-F-conjunto-top-shorts-feminino-los-angeles-slim-moda-academia.webp</t>
-  </si>
-  <si>
-    <t>Kit Conjunto Fitness Feminino + Camiseta Roupa Academia Roxo Lisa M</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_841583-MLB89985983942_082025-F.webp</t>
-  </si>
-  <si>
-    <t>Kit 5 Camisa Masculina Termica Academia Dry Fit Malha Fria</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_997360-MLB89836875348_082025-F-kit-5-camisa-masculina-termica-academia-dry-fit-malha-fria.webp</t>
-  </si>
-  <si>
-    <t>Lâmpada Led Taschibra Bulbo 15w Branco Frio 6500k Luz Branco-frio</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_961028-MLU78230092907_082024-F.webp</t>
-  </si>
-  <si>
-    <t>Bicicleta Ergométrica Bike Academia Spinning X11 cor preto e vermelho</t>
-  </si>
-  <si>
-    <t>Conjunto De Mesa Com 4 Cadeiras + Guarda Sol Piscina Jardim</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_879619-MLB101681386902_122025-F-conjunto-de-mesa-com-4-cadeiras-guarda-sol-piscina-jardim.webp</t>
-  </si>
-  <si>
-    <t>Smart Tag Compatível Find My Airtag Gps Rastreador Objetos Preto</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_806966-MLA105981916235_012026-F.webp</t>
-  </si>
-  <si>
-    <t>Eletronicos</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_788270-MLB85613415884_062025-F-headphone-bluetooth-reduco-de-ruido-do-anc-com-microfone-f5.webp</t>
-  </si>
-  <si>
-    <t>Headphone Bluetooth Redução De Ruído Do Anc Com Microfone F5</t>
-  </si>
-  <si>
-    <t>Jaleco Avental Botão Feminino Oxford Com Punho E Manga Longa</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_656171-MLB89388767014_082025-F-jaleco-avental-boto-feminino-oxford-com-punho-e-manga-longa.webp</t>
-  </si>
-  <si>
-    <t>Roupas</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_963509-MLB104684972076_012026-F.webp</t>
-  </si>
-  <si>
-    <t>Roku Streaming Stick 2025 Para Tv Hd/fhd Controle Por Voz Preto De Voz</t>
-  </si>
-  <si>
-    <t>Presente Natura Tododia Sabonetes em Barra Sortidos 5un 90G</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_776711-MLA92278973180_092025-F.webp</t>
-  </si>
-  <si>
-    <t>Kit Moedor De Pés Automático Recarregável Usb Lixa De Pé</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_995783-MLB102098428340_122025-F-kit-moedor-de-pes-automatico-recarregavel-usb-lixa-de-pe.webp</t>
-  </si>
-  <si>
-    <t>Quebra Sol Para Brisa Carro Protetor Solar Quebra Sol</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_998002-MLB90623040455_082025-F.webp</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_796878-MLA88041903272_072025-F.webp</t>
-  </si>
-  <si>
-    <t>Sorveteira Ninja Creami</t>
-  </si>
-  <si>
-    <t>Cabo Usb Plus Turbo Tipo C Compativel Com Samsung Galaxy S25 S24 Plus S23 Fe S22 S21 S20 A16 A15 A22 A13 A14 A55 A53 A54 A06 A05s A20 A21 Apple iPhone 17 16 15 Carplay Auto Android</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_626755-MLA105599427615_012026-F.webp</t>
-  </si>
-  <si>
-    <t>Nautica Voyage Edt 50ml Para Masculino</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_976778-MLA88319852853_072025-F.webp</t>
-  </si>
-  <si>
-    <t>Cuidado Pessoais</t>
-  </si>
-  <si>
-    <t>Paris Elysees Vodka Wild EDT 100ml para masculino</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_970885-MLA84177076022_052025-F.webp</t>
-  </si>
-  <si>
-    <t>Perfume Natura Kaiak Extreme Deo colônia 100 ml</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_964055-MLA84536043026_052025-F.webp</t>
-  </si>
-  <si>
-    <t>Kit 10 Pares Meias Mash Invisível Esportiva Algodão Original</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_897046-MLB98663774114_112025-F-kit-10-pares-meias-mash-invisivel-esportiva-algodo-original.webp</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_877493-MLA99478951284_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Moedor Café Triturador Elétrico De Grãos Sementes Ervas Usb Cor Preto</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_965103-MLA99575749404_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Chaleira Eletrica Atacama 1,8l - Unitermi</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_651826-MLA99986263335_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Mixer Turbo Chef 3 Em 1 200w Triturador E Fuet Elgin</t>
-  </si>
-  <si>
-    <t>Filtro De Café Reutilizável Em Aço Inox Modelo 103 Peneira Permanente Sustentável Coar Café Tradicional Sem Papel Econômico E Durável Ponte Lar Utilidades</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_803581-MLA99564243074_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Jogo Talheres Faqueiro Búzios Aço Inox 24 Peças Tramontina</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_885228-MLA105354697197_012026-F.webp</t>
-  </si>
-  <si>
-    <t>Drone Mini Pro Câmera 4k Com Gps 2 Baterias Completo Com Assistente De Pouso E Sensores De Obstáculos + Maleta De Transporte Drone Preto</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_974939-MLA99533870508_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Smart Tv U8600f Crystal Uhd 4k 50 2025 Preto Samsung</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_673180-MLA99945056215_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Tênis Masculino Feminino Kappa Park 2.0 Original</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_881886-MLB105747673925_012026-F-tnis-masculino-feminino-kappa-park-20-original.webp</t>
-  </si>
-  <si>
-    <t>Console Playstation 5 Slim Edição Digital 825 Gb</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_677584-MLA99572203884_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Games</t>
-  </si>
-  <si>
-    <t>Aspirador de Pó Vertical e Portátil WAP High Speed Plus 1350W 3 em 1</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_887734-MLA99375017938_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Purificador De Água Electrolux Pure4x Pe12 Cor Branco</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_681123-MLA99453121194_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Graxa Lubrificante Para Correntes Chain Lub super Moto 200mL - Mobil</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_760097-MLA102137161656_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Comunicador Capacete V6 Plus 2 Unidades / Par Bluetooth 5.0</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_667088-MLB103999766319_012026-F-comunicador-capacete-v6-plus-2-unidades-par-bluetooth-50.webp</t>
-  </si>
-  <si>
-    <t>Válvula Para Caixa Dágua Duchão Blukit Com Dupla Retenção 5 m</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_992216-MLA99964861387_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Fechadura Eletronica Digital Com Biometria, Senha, Cartão Ic E Tuya App Bluetooth LAZORO</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_787439-MLA104930046625_012026-F.webp</t>
-  </si>
-  <si>
-    <t>Máquina Fabricadora De Gelo 15kg Portátil Oninstek Cor Preto</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_907453-MLA92604606921_092025-F.webp</t>
-  </si>
-  <si>
-    <t>Bt-777239 Pipoqueira Elétrica Sem Óleo Máquina Fazer Pipoca Ar Quente 110v</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_757387-MLA99940407373_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Cooktop Indução Eletrico 2 Bocas Vidro Preto Trava Segurança</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_957403-MLA102883063095_122025-F.webp</t>
-  </si>
-  <si>
-    <t>Adaptador De Fogão De Indução Difusor Conversor Chapa Induçã Prateado</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_835336-MLB104060575249_012026-F.webp</t>
-  </si>
-  <si>
-    <t>Kit 5 Chumbinho Snyper Diabolô 5.5mm (promoção)</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_901992-MLA49833296518_052022-F.webp</t>
-  </si>
-  <si>
-    <t>https://meli.la/21cXEcY</t>
-  </si>
-  <si>
-    <t>https://meli.la/2CPkNmk</t>
-  </si>
-  <si>
-    <t>https://meli.la/1y6fcNW</t>
-  </si>
-  <si>
-    <t>https://meli.la/1ZCKd41</t>
-  </si>
-  <si>
-    <t>https://meli.la/2Y7yAuu</t>
-  </si>
-  <si>
-    <t>https://meli.la/11V2esF</t>
-  </si>
-  <si>
-    <t>https://meli.la/1bEdwq6</t>
-  </si>
-  <si>
-    <t>https://meli.la/27CLU9a</t>
-  </si>
-  <si>
-    <t>https://meli.la/18dKknW</t>
-  </si>
-  <si>
-    <t>https://meli.la/19BZz5R</t>
-  </si>
-  <si>
-    <t>https://meli.la/1PXZbc3</t>
-  </si>
-  <si>
-    <t>https://meli.la/1btb7mZ</t>
-  </si>
-  <si>
-    <t>https://meli.la/11YMRyc</t>
-  </si>
-  <si>
-    <t>https://meli.la/11gEiZd</t>
-  </si>
-  <si>
-    <t>https://meli.la/2rZnJwR</t>
-  </si>
-  <si>
-    <t>https://meli.la/22ueKjd</t>
-  </si>
-  <si>
-    <t>https://meli.la/2dZDfGD</t>
-  </si>
-  <si>
-    <t>https://meli.la/1sSq3Yb</t>
-  </si>
-  <si>
-    <t>https://meli.la/2PvVt1v</t>
-  </si>
-  <si>
-    <t>https://meli.la/2hmw4vM</t>
-  </si>
-  <si>
-    <t>https://meli.la/1tj9PsH</t>
-  </si>
-  <si>
-    <t>https://meli.la/2vMQmuU</t>
-  </si>
-  <si>
-    <t>https://meli.la/2t2YYkG</t>
-  </si>
-  <si>
-    <t>https://meli.la/1Hvu5z8</t>
-  </si>
-  <si>
-    <t>https://meli.la/2WeFR34</t>
-  </si>
-  <si>
-    <t>https://meli.la/2esx5Kd</t>
-  </si>
-  <si>
-    <t>https://meli.la/2GEswZw</t>
-  </si>
-  <si>
-    <t>https://meli.la/2tKkeid</t>
-  </si>
-  <si>
-    <t>https://meli.la/1WvcnqX</t>
-  </si>
-  <si>
-    <t>https://meli.la/2J2CriG</t>
-  </si>
-  <si>
-    <t>https://meli.la/1QmhH6z</t>
-  </si>
-  <si>
-    <t>https://meli.la/1jpBfhb</t>
-  </si>
-  <si>
-    <t>https://meli.la/1BQmqfU</t>
-  </si>
-  <si>
-    <t>https://meli.la/25Kha96</t>
-  </si>
-  <si>
-    <t>https://meli.la/2nzvgYf</t>
-  </si>
-  <si>
-    <t>https://meli.la/18FZ6ki</t>
-  </si>
-  <si>
-    <t>https://meli.la/2fZRSnJ</t>
-  </si>
-  <si>
-    <t>https://meli.la/1sBEVL5</t>
-  </si>
-  <si>
-    <t>https://meli.la/2bvumfG</t>
-  </si>
-  <si>
-    <t>https://meli.la/2smh87H</t>
-  </si>
-  <si>
-    <t>https://meli.la/2DLpW5Q</t>
-  </si>
-  <si>
-    <t>https://meli.la/1EkqyuM</t>
-  </si>
-  <si>
-    <t>https://meli.la/1rD8F3M</t>
-  </si>
-  <si>
-    <t>https://meli.la/22T72GS</t>
-  </si>
-  <si>
-    <t>https://meli.la/1UEKC3s</t>
-  </si>
-  <si>
-    <t>https://meli.la/16r3ju1</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_936974-MLA99394285476_112025-F.webp</t>
-  </si>
-  <si>
-    <t>https://meli.la/1MYtETr</t>
-  </si>
-  <si>
-    <t>https://meli.la/19ddomp</t>
-  </si>
-  <si>
-    <t>https://meli.la/18ADTfp</t>
-  </si>
-  <si>
-    <t>https://meli.la/1GjXrYY</t>
-  </si>
-  <si>
-    <t>https://meli.la/1PR9G7q</t>
-  </si>
-  <si>
-    <t>https://meli.la/1weGFWB</t>
-  </si>
-  <si>
-    <t>https://meli.la/22gTvbC</t>
-  </si>
-  <si>
-    <t>https://meli.la/2oTrBuB</t>
-  </si>
-  <si>
-    <t>https://meli.la/2eGB3ZS</t>
-  </si>
-  <si>
-    <t>https://meli.la/28zwg9R</t>
-  </si>
-  <si>
-    <t>https://meli.la/1rwS7Wu</t>
-  </si>
-  <si>
-    <t>https://meli.la/2arH4rY</t>
-  </si>
-  <si>
-    <t>https://meli.la/1AfFvv9</t>
-  </si>
-  <si>
-    <t>https://meli.la/2mPjbiD</t>
-  </si>
-  <si>
-    <t>https://meli.la/2TKmFTZ</t>
-  </si>
-  <si>
-    <t>https://meli.la/1ZzCasp</t>
-  </si>
-  <si>
-    <t>https://meli.la/2EnnEaL</t>
-  </si>
-  <si>
-    <t>https://meli.la/1Vm89PB</t>
-  </si>
-  <si>
-    <t>https://meli.la/1o1SAyE</t>
-  </si>
-  <si>
-    <t>https://meli.la/2srmvpJ</t>
-  </si>
-  <si>
-    <t>https://meli.la/17DcsTC</t>
-  </si>
-  <si>
-    <t>https://meli.la/2n2mk5m</t>
-  </si>
-  <si>
-    <t>https://meli.la/2M4PEBk</t>
-  </si>
-  <si>
-    <t>https://meli.la/1kh7BDX</t>
-  </si>
-  <si>
-    <t>https://meli.la/2wsyKs6</t>
-  </si>
-  <si>
-    <t>https://meli.la/1RX25hU</t>
-  </si>
-  <si>
-    <t>https://meli.la/1pieq5F</t>
-  </si>
-  <si>
-    <t>https://meli.la/2nCX9ri</t>
-  </si>
-  <si>
-    <t>https://meli.la/2yucFU1</t>
-  </si>
-  <si>
-    <t>https://meli.la/1xz4tJF</t>
-  </si>
-  <si>
-    <t>https://meli.la/1Bqa2VC</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_910534-MLA99831868899_112025-F.webp</t>
-  </si>
-  <si>
-    <t>Escova de limpeza elétrica 12 em 1 giratória recarregável cabo regulável EPS-4112 - Branco</t>
-  </si>
-  <si>
-    <t>https://meli.la/1RhSueu</t>
-  </si>
-  <si>
-    <t>https://meli.la/1yztVbP</t>
-  </si>
-  <si>
-    <t>https://meli.la/1LEeuwY</t>
-  </si>
-  <si>
-    <t>https://meli.la/23SuRfp</t>
-  </si>
-  <si>
-    <t>https://meli.la/2ZZFc2P</t>
+    <t>https://m.media-amazon.com/images/I/41uUYcqfLxL._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>Apple iPhone 16 (256 GB) – Preto</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4bhs77B</t>
+  </si>
+  <si>
+    <t>Eletrônicos</t>
+  </si>
+  <si>
+    <t>Fire TV Stick HD (Geração mais recente) | Com controle remoto por voz com Alexa (inclui comandos de TV), controles de casa inteligente e streaming em HD</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61K7fAOac9L._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3MT6Wka</t>
+  </si>
+  <si>
+    <t>Roku Streaming Stick HD 2025 | Dispositivo de streaming para TV HD/FHD com controle remoto por comando de voz compatível com Alexa, Siri e Google</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71NIAAVDxML._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4bhshMf</t>
+  </si>
+  <si>
+    <t>Aperitivo Bitter Campari 748ml</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71a8-9BtUVL._AC_SX522_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/40Q0ZaK</t>
+  </si>
+  <si>
+    <t>Bebidas</t>
+  </si>
+  <si>
+    <t>Filamento PLA Vermelho Premium 1kg, 1.75Mm, Para Impressoras 3D - Voolt3D</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61IGgSj4xDL._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4u7rFBk</t>
+  </si>
+  <si>
+    <t>Impressão 3D</t>
+  </si>
+  <si>
+    <t>Samsung Combo Smart TV 58" Crystal UHD 4K U8500F 2025 + Soundbar Samsung HW-B400F</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51lHYeST6eL._AC_SX522_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4rkQA1N</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51MV8w-DQmS._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>Lava Louças 14 Serviços Preto 220V Midea</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4d40qS8</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/7106NYA4Z2L._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>Ninja Creami Sorveteira 127v - Máquina de sobremesa geladas para Gelato, Milkshakes, Sorvetes, Tigelas de Smoothie</t>
+  </si>
+  <si>
+    <t>https://amzn.to/47yyke6</t>
+  </si>
+  <si>
+    <t>Máquina de Gelo Eos 12kg Ice Compact Inox All Black Emg06p 220v</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51sQ59gcOGL._SX522_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/47iBuCE</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/517itypmYaL._AC_SY879_.jpg</t>
+  </si>
+  <si>
+    <t>Pilha Alcalina AAA com 16 unidades Elgin Palito</t>
+  </si>
+  <si>
+    <t>https://amzn.to/40eGnZJ</t>
+  </si>
+  <si>
+    <t>WAP Ventilador de Torre AIR SILENCE com 4 Ní­veis de Velocidade, Time de até 15 Horas e Desligamento Automático 127V</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71TNRBwT+GL._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4soCCg4</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/616wWGrxpYL._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>DREAME L40 Ultra AE Robô Aspirador e Mopa, Sucção 19.000Pa, Caixa de Poeira Autoesvaziável, Mopa Flexível com Lavagem Automática 74°C, Amigo dos Pets, App/Voz(Alexa/Google/Siri), 127v</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4s19D2i</t>
+  </si>
+  <si>
+    <t>Creality K1C Impressora 3D 600 mm/s Câmera Al de alta velocidade Extrusora de acionamento direto de metal com nivelamento automático adequado para filamentos de fibra de carbono</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/615goFZOt7L._AC_SX522_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4rCePsB</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61stBLx-KhL._AC_SX522_.jpg</t>
+  </si>
+  <si>
+    <t>JBL Caixa de Som, Boombox 3, Bluetooth, À Prova D'água e Poeira - Preto</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4rWUy1D</t>
+  </si>
+  <si>
+    <t>Gravador a laser Twotrees TTS55 Pro 40W Máquina de gravação a laser Placa-mãe de 32 bits, para madeira compensada cortada e gravação em alumínio, Potência do laser: 5,5 W, Área de gravação: 300x300mm</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81PdYPnyC-L._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/40ibUdi</t>
+  </si>
+  <si>
+    <t>Esfregão Elétrico Profissional 9 em 1 Recarregável Mop 360º Sem Fio Potente Portátil Limpeza Pesada Banheiro Cozinha Piso Azulejo Janela Escova Multiuso Compacto Giratório Casa Premium Ajustavel</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51j7RW0lQeL._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4baTwYB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -902,6 +251,12 @@
     <font>
       <sz val="17"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF0F1111"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -964,9 +319,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -990,6 +342,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1014,13 +369,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1062,13 +417,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1110,13 +465,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>49212</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1158,14 +513,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>120954</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1206,14 +561,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1254,13 +609,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1302,14 +657,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>431195</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1350,14 +705,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>189279</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>189278</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1398,13 +753,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1446,13 +801,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1494,13 +849,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>154</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1556,13 +911,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>156</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1605,13 +960,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>49212</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1653,14 +1008,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>120954</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1701,14 +1056,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1749,13 +1104,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1797,14 +1152,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>431195</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1845,14 +1200,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>189279</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>189278</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1893,13 +1248,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1941,13 +1296,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1989,13 +1344,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>154</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2051,13 +1406,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>156</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2100,13 +1455,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2148,13 +1503,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2196,14 +1551,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>120953</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2244,13 +1599,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2292,14 +1647,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95854</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2340,13 +1695,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2388,14 +1743,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2436,13 +1791,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2484,13 +1839,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2532,13 +1887,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2580,13 +1935,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>168</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2628,13 +1983,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>169</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>171</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2676,13 +2031,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>171</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>195</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2724,13 +2079,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>196</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2786,13 +2141,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2834,14 +2189,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>120953</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2882,13 +2237,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2930,14 +2285,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95854</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2978,13 +2333,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3026,14 +2381,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3074,13 +2429,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3122,13 +2477,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3170,13 +2525,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3218,13 +2573,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>168</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3266,13 +2621,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>169</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>171</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3314,13 +2669,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>171</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>195</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3362,13 +2717,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>196</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3424,13 +2779,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3472,14 +2827,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>120953</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3520,13 +2875,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3568,14 +2923,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95854</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3616,13 +2971,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3664,14 +3019,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3712,13 +3067,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3760,13 +3115,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3808,13 +3163,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3856,13 +3211,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>168</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3904,13 +3259,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>169</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>171</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3952,13 +3307,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>171</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>195</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4000,13 +3355,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>196</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4062,14 +3417,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4110,14 +3465,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4158,14 +3513,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4206,14 +3561,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4254,14 +3609,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4586,7 +3941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D200"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="164" bestFit="1" customWidth="1"/>
@@ -4611,1530 +3966,539 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="5"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="5"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="3"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="3"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="3"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="3"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="3"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="3"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="3"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="3"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="3"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="3"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="3"/>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="6"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="6"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="116" spans="1:1" ht="21.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="10" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>198</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>199</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" t="s">
-        <v>200</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>201</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>203</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>204</v>
-      </c>
-      <c r="D15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" t="s">
-        <v>206</v>
-      </c>
-      <c r="D17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" t="s">
-        <v>207</v>
-      </c>
-      <c r="D18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>208</v>
-      </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" t="s">
-        <v>209</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" t="s">
-        <v>210</v>
-      </c>
-      <c r="D21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" t="s">
-        <v>272</v>
-      </c>
-      <c r="D22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" t="s">
-        <v>211</v>
-      </c>
-      <c r="D23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" t="s">
-        <v>212</v>
-      </c>
-      <c r="D24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" t="s">
-        <v>273</v>
-      </c>
-      <c r="D25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" t="s">
-        <v>213</v>
-      </c>
-      <c r="D26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" t="s">
-        <v>214</v>
-      </c>
-      <c r="D27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>215</v>
-      </c>
-      <c r="D28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" t="s">
-        <v>216</v>
-      </c>
-      <c r="D29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>72</v>
-      </c>
-      <c r="B30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" t="s">
-        <v>217</v>
-      </c>
-      <c r="D30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" t="s">
-        <v>218</v>
-      </c>
-      <c r="D31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" t="s">
-        <v>219</v>
-      </c>
-      <c r="D32" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" t="s">
-        <v>220</v>
-      </c>
-      <c r="D33" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>221</v>
-      </c>
-      <c r="D34" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>85</v>
-      </c>
-      <c r="B35" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" t="s">
-        <v>222</v>
-      </c>
-      <c r="D35" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s">
-        <v>223</v>
-      </c>
-      <c r="D36" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" t="s">
-        <v>224</v>
-      </c>
-      <c r="D37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" t="s">
-        <v>225</v>
-      </c>
-      <c r="D38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B39" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" t="s">
-        <v>226</v>
-      </c>
-      <c r="D39" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" t="s">
-        <v>227</v>
-      </c>
-      <c r="D40" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C41" t="s">
-        <v>228</v>
-      </c>
-      <c r="D41" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>100</v>
-      </c>
-      <c r="B42" t="s">
-        <v>101</v>
-      </c>
-      <c r="C42" t="s">
-        <v>229</v>
-      </c>
-      <c r="D42" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>102</v>
-      </c>
-      <c r="B43" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" t="s">
-        <v>230</v>
-      </c>
-      <c r="D43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" t="s">
-        <v>105</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D44" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>106</v>
-      </c>
-      <c r="B45" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" t="s">
-        <v>232</v>
-      </c>
-      <c r="D45" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D46" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>110</v>
-      </c>
-      <c r="B47" t="s">
-        <v>111</v>
-      </c>
-      <c r="C47" t="s">
-        <v>274</v>
-      </c>
-      <c r="D47" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>112</v>
-      </c>
-      <c r="B48" t="s">
-        <v>113</v>
-      </c>
-      <c r="C48" t="s">
-        <v>234</v>
-      </c>
-      <c r="D48" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>114</v>
-      </c>
-      <c r="B49" t="s">
-        <v>115</v>
-      </c>
-      <c r="C49" t="s">
-        <v>235</v>
-      </c>
-      <c r="D49" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>118</v>
-      </c>
-      <c r="B50" t="s">
-        <v>237</v>
-      </c>
-      <c r="C50" t="s">
-        <v>236</v>
-      </c>
-      <c r="D50" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" t="s">
-        <v>120</v>
-      </c>
-      <c r="C51" t="s">
-        <v>238</v>
-      </c>
-      <c r="D51" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>121</v>
-      </c>
-      <c r="B52" t="s">
-        <v>122</v>
-      </c>
-      <c r="C52" t="s">
-        <v>239</v>
-      </c>
-      <c r="D52" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>125</v>
-      </c>
-      <c r="B53" t="s">
-        <v>124</v>
-      </c>
-      <c r="C53" t="s">
-        <v>240</v>
-      </c>
-      <c r="D53" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>126</v>
-      </c>
-      <c r="B54" t="s">
-        <v>127</v>
-      </c>
-      <c r="C54" t="s">
-        <v>241</v>
-      </c>
-      <c r="D54" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>130</v>
-      </c>
-      <c r="B55" t="s">
-        <v>129</v>
-      </c>
-      <c r="C55" t="s">
-        <v>242</v>
-      </c>
-      <c r="D55" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>131</v>
-      </c>
-      <c r="B56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C56" t="s">
-        <v>243</v>
-      </c>
-      <c r="D56" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>133</v>
-      </c>
-      <c r="B57" t="s">
-        <v>134</v>
-      </c>
-      <c r="C57" t="s">
-        <v>275</v>
-      </c>
-      <c r="D57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>135</v>
-      </c>
-      <c r="B58" t="s">
-        <v>136</v>
-      </c>
-      <c r="C58" t="s">
-        <v>244</v>
-      </c>
-      <c r="D58" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>138</v>
-      </c>
-      <c r="B59" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>139</v>
-      </c>
-      <c r="B60" t="s">
-        <v>140</v>
-      </c>
-      <c r="C60" t="s">
-        <v>245</v>
-      </c>
-      <c r="D60" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>141</v>
-      </c>
-      <c r="B61" t="s">
-        <v>142</v>
-      </c>
-      <c r="C61" t="s">
-        <v>246</v>
-      </c>
-      <c r="D61" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>144</v>
-      </c>
-      <c r="B62" t="s">
-        <v>145</v>
-      </c>
-      <c r="C62" t="s">
-        <v>247</v>
-      </c>
-      <c r="D62" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>146</v>
-      </c>
-      <c r="B63" t="s">
-        <v>147</v>
-      </c>
-      <c r="C63" t="s">
-        <v>248</v>
-      </c>
-      <c r="D63" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>148</v>
-      </c>
-      <c r="B64" t="s">
-        <v>149</v>
-      </c>
-      <c r="C64" t="s">
-        <v>249</v>
-      </c>
-      <c r="D64" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>151</v>
-      </c>
-      <c r="B65" t="s">
-        <v>150</v>
-      </c>
-      <c r="C65" t="s">
-        <v>191</v>
-      </c>
-      <c r="D65" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>153</v>
-      </c>
-      <c r="B66" t="s">
-        <v>152</v>
-      </c>
-      <c r="C66" t="s">
-        <v>250</v>
-      </c>
-      <c r="D66" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>155</v>
-      </c>
-      <c r="B67" t="s">
-        <v>154</v>
-      </c>
-      <c r="C67" t="s">
-        <v>251</v>
-      </c>
-      <c r="D67" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>156</v>
-      </c>
-      <c r="B68" t="s">
-        <v>157</v>
-      </c>
-      <c r="C68" t="s">
-        <v>252</v>
-      </c>
-      <c r="D68" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>158</v>
-      </c>
-      <c r="B69" t="s">
-        <v>159</v>
-      </c>
-      <c r="C69" t="s">
-        <v>253</v>
-      </c>
-      <c r="D69" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>160</v>
-      </c>
-      <c r="B70" t="s">
-        <v>161</v>
-      </c>
-      <c r="C70" t="s">
-        <v>254</v>
-      </c>
-      <c r="D70" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>162</v>
-      </c>
-      <c r="B71" t="s">
-        <v>163</v>
-      </c>
-      <c r="C71" t="s">
-        <v>255</v>
-      </c>
-      <c r="D71" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>164</v>
-      </c>
-      <c r="B72" t="s">
-        <v>165</v>
-      </c>
-      <c r="C72" t="s">
-        <v>256</v>
-      </c>
-      <c r="D72" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>166</v>
-      </c>
-      <c r="B73" t="s">
-        <v>167</v>
-      </c>
-      <c r="C73" t="s">
-        <v>257</v>
-      </c>
-      <c r="D73" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>169</v>
-      </c>
-      <c r="B74" t="s">
-        <v>170</v>
-      </c>
-      <c r="C74" t="s">
-        <v>258</v>
-      </c>
-      <c r="D74" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>171</v>
-      </c>
-      <c r="B75" t="s">
-        <v>172</v>
-      </c>
-      <c r="C75" t="s">
-        <v>259</v>
-      </c>
-      <c r="D75" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>173</v>
-      </c>
-      <c r="B76" t="s">
-        <v>174</v>
-      </c>
-      <c r="C76" t="s">
-        <v>260</v>
-      </c>
-      <c r="D76" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>175</v>
-      </c>
-      <c r="B77" t="s">
-        <v>176</v>
-      </c>
-      <c r="C77" t="s">
-        <v>261</v>
-      </c>
-      <c r="D77" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>177</v>
-      </c>
-      <c r="B78" t="s">
-        <v>178</v>
-      </c>
-      <c r="C78" t="s">
-        <v>262</v>
-      </c>
-      <c r="D78" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>179</v>
-      </c>
-      <c r="B79" t="s">
-        <v>180</v>
-      </c>
-      <c r="C79" t="s">
-        <v>263</v>
-      </c>
-      <c r="D79" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>181</v>
-      </c>
-      <c r="B80" t="s">
-        <v>182</v>
-      </c>
-      <c r="C80" t="s">
-        <v>264</v>
-      </c>
-      <c r="D80" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>183</v>
-      </c>
-      <c r="B81" t="s">
-        <v>184</v>
-      </c>
-      <c r="C81" t="s">
-        <v>265</v>
-      </c>
-      <c r="D81" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>185</v>
-      </c>
-      <c r="B82" t="s">
-        <v>186</v>
-      </c>
-      <c r="C82" t="s">
-        <v>266</v>
-      </c>
-      <c r="D82" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>187</v>
-      </c>
-      <c r="B83" t="s">
-        <v>188</v>
-      </c>
-      <c r="C83" t="s">
-        <v>267</v>
-      </c>
-      <c r="D83" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>189</v>
-      </c>
-      <c r="B84" t="s">
-        <v>190</v>
-      </c>
-      <c r="C84" t="s">
-        <v>268</v>
-      </c>
-      <c r="D84" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>270</v>
-      </c>
-      <c r="B85" t="s">
-        <v>269</v>
-      </c>
-      <c r="C85" t="s">
-        <v>271</v>
-      </c>
-      <c r="D85" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="10"/>
-    </row>
-    <row r="90" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="5"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="4"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="4"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="4"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="4"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="4"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="4"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="4"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="4"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="4"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="4"/>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="4"/>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="4"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="4"/>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="4"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="4"/>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="4"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="4"/>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="4"/>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="4"/>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="4"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="4"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="4"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="6"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="6"/>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="4"/>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="5"/>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="4"/>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="4"/>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="4"/>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="4"/>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="4"/>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="4"/>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="4"/>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="4"/>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="4"/>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="4"/>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="4"/>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="4"/>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="4"/>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="4"/>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="4"/>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="4"/>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="4"/>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="4"/>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="4"/>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="4"/>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="4"/>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="4"/>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="6"/>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="6"/>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="4"/>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="5"/>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="4"/>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="4"/>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="4"/>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="4"/>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="4"/>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="4"/>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="4"/>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="4"/>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="4"/>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="4"/>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="4"/>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="4"/>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="4"/>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="4"/>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="4"/>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="4"/>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="4"/>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="4"/>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="4"/>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="4"/>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="4"/>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="4"/>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="4"/>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="6"/>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="6"/>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="4"/>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="5"/>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="4"/>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="4"/>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="4"/>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="4"/>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="4"/>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="4"/>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="4"/>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="4"/>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="4"/>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="4"/>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="4"/>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="4"/>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="4"/>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="4"/>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="4"/>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="4"/>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="4"/>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="4"/>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="4"/>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="4"/>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="4"/>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="4"/>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="4"/>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="7"/>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="7"/>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" ht="21.75" x14ac:dyDescent="0.25">
-      <c r="A200" s="11" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{DCE316A2-6F5F-4239-8670-A2501AD068BA}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{E75C36C1-9EBF-4C4A-9D5E-6178C36287DA}"/>
-    <hyperlink ref="B9" r:id="rId3" xr:uid="{E7AF4AD0-FB67-4D18-A345-7AC735B2DDD9}"/>
-    <hyperlink ref="B10" r:id="rId4" xr:uid="{5ED3D7ED-FC6D-4C44-8B5F-671739F6A728}"/>
-    <hyperlink ref="B14" r:id="rId5" xr:uid="{AED35A75-AE1C-4AD0-9122-E943C0451F4B}"/>
-    <hyperlink ref="A198" r:id="rId6" location="redirect=landing_international&amp;origin=vip" display="https://www.mercadolivre.com.br/importados/compra-internacional - redirect=landing_international&amp;origin=vip" xr:uid="{CC0DCAE0-A290-49ED-AC96-9E0C27938302}"/>
-    <hyperlink ref="B77" r:id="rId7" xr:uid="{C44C884A-2B1F-46D5-849E-2AEEA7727C26}"/>
-    <hyperlink ref="C46" r:id="rId8" xr:uid="{D7CE1F55-B7E3-4E3A-87FB-E2DE297FF331}"/>
+    <hyperlink ref="A114" r:id="rId1" location="redirect=landing_international&amp;origin=vip" display="https://www.mercadolivre.com.br/importados/compra-internacional - redirect=landing_international&amp;origin=vip" xr:uid="{CC0DCAE0-A290-49ED-AC96-9E0C27938302}"/>
+    <hyperlink ref="B12" r:id="rId2" xr:uid="{F5A0C3FF-26B9-4A83-B372-E21DC2C43072}"/>
+    <hyperlink ref="B16" r:id="rId3" xr:uid="{73E8B330-11AE-41FE-8E9C-DD103415022E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
-  <drawing r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
--- a/products.xlsx
+++ b/products.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\Amazon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193F5692-5344-4438-BDBB-06BE0FA03AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B120DEF9-B69B-4495-8AAA-F913B1551447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="79">
   <si>
     <t>name</t>
   </si>
@@ -197,13 +197,73 @@
   </si>
   <si>
     <t>https://amzn.to/4baTwYB</t>
+  </si>
+  <si>
+    <t>Bolsa para Lavar Tênis na Máquina com Zíper Reforçado – Saco Protetor de Sapatos para Lavadora e Secadora, Malha Chenille Resistente, Reutilizável e Compatível com Todos os Modelos</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61fQfHOgOUL._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4e8SDD5</t>
+  </si>
+  <si>
+    <t>Tábua de Corte Profissional em Aço Inoxidável 46 x 30 cm – Retangular, Higiênica e Ideal para Cozinha</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61c5jtrbY5L._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/41XvRGQ</t>
+  </si>
+  <si>
+    <t>Cozinha</t>
+  </si>
+  <si>
+    <t>Tábua de Corte Dupla Face Inox e PP Antibacteriana – Tábua de Carne em Aço Inoxidável Antimicrobiana, Antiderrapante, Resistente a Mofo e Arranhões – Tamanho Grande Premium Tam. 38x26x1,2cm</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51aT2SRd+pL._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4t9crL6</t>
+  </si>
+  <si>
+    <t>Protetor de Papel para Air Fryer Forma Quadrada (100 Unidades) Papel Forro Descartável Antiaderente Resistente a Calor e Óleo Praticidade Total para Cozinha Descartável para Fritadeira Elétrica</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61rMEb41T5L._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4mjzvEH</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61wvVk465pL._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4cuvERz</t>
+  </si>
+  <si>
+    <t>Pastilha Bactericida Aromatizante para Ar Condicionado Split – FLOR DE ALGODÃO (25g) Higienizadora Ação Neutralizadora de odores Aroma Contínuo ELIMINA MAU CHEIRO</t>
+  </si>
+  <si>
+    <t>Tênis Masculino para Corrida Academia e Caminhada Leve Macio e Esportivo</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61cQ2YSegQL._AC_SY695_.jpg</t>
+  </si>
+  <si>
+    <t>https://amzn.to/41kZNwr</t>
+  </si>
+  <si>
+    <t>Moda</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,6 +320,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF565959"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -312,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -345,6 +411,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -519,8 +588,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>120954</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>514050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -711,8 +780,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>189278</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>68325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -760,7 +829,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -808,7 +877,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -856,7 +925,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1014,8 +1083,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>120954</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>514050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1206,8 +1275,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>189278</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>68325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1255,7 +1324,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1303,7 +1372,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1351,7 +1420,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1557,8 +1626,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>120953</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>514049</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1653,8 +1722,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>95854</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>488950</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1749,8 +1818,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>332620</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1846,7 +1915,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1894,7 +1963,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1942,7 +2011,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2086,7 +2155,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2195,8 +2264,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>120953</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>514049</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2291,8 +2360,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>95854</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>488950</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2387,8 +2456,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>332620</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2484,7 +2553,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2532,7 +2601,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2580,7 +2649,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2724,7 +2793,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2833,8 +2902,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>120953</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>514049</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2929,8 +2998,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>95854</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>488950</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3025,8 +3094,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>332620</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3122,7 +3191,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3170,7 +3239,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3218,7 +3287,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3362,7 +3431,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4188,23 +4257,89 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
+    <row r="18" spans="1:4" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="69.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>

--- a/products.xlsx
+++ b/products.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\Amazon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B120DEF9-B69B-4495-8AAA-F913B1551447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBDFA18-E5CE-4FF5-9346-C4944D5B64A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="113">
   <si>
     <t>name</t>
   </si>
@@ -257,6 +257,108 @@
   </si>
   <si>
     <t>Moda</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3RhqUGM</t>
+  </si>
+  <si>
+    <t>Promoção</t>
+  </si>
+  <si>
+    <t>Compre 2 Lancôme e leve 15% off</t>
+  </si>
+  <si>
+    <t>Compre R$ 80 NIVEA, leve 20% off</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4w1UL6l</t>
+  </si>
+  <si>
+    <t>15% off em L'Oréal Professional</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4n2PSWe</t>
+  </si>
+  <si>
+    <t>15% off em Mantecorp</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4utZSL0</t>
+  </si>
+  <si>
+    <t>20% off em roupas esportivas</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4eYzzI5</t>
+  </si>
+  <si>
+    <t>20% off em Esporte até R$ 150off</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4d5ZDi3</t>
+  </si>
+  <si>
+    <t>20% off em calçados</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4uuBQzr</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/173._CB772140680_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/5do5/lamcome._CB780163372_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/loreal._CB785876032_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/mantecorp_1._CB781932258_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/modaEP._CB783803354_UC432,290_.png</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/186._CB772491595_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/vestuario_EP._CB781931634_UC432,290_.png</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/eletronicos10ff._CB785986151_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/jogos._CB781932180_UC432,290_.png</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/BRINOX_1._CB785900558_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/kitchen._CB784221136_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>10% off em Eletrônicos</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4tQizbN</t>
+  </si>
+  <si>
+    <t>30% off em Brinquedos</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4up5FkD</t>
+  </si>
+  <si>
+    <t>20% off em Construção</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4n30hRQ</t>
+  </si>
+  <si>
+    <t>https://amzn.to/42bG9Dy</t>
+  </si>
+  <si>
+    <t>20% off em Cozinha</t>
   </si>
 </sst>
 </file>
@@ -780,8 +882,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>68325</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>147923</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -829,7 +931,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -877,7 +979,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>187023</xdr:rowOff>
+      <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1275,8 +1377,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>68325</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>147923</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1324,7 +1426,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1372,7 +1474,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>187023</xdr:rowOff>
+      <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1866,8 +1968,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>136151</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1914,8 +2016,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>98053</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1963,7 +2065,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2011,7 +2113,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>187023</xdr:rowOff>
+      <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2155,7 +2257,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2504,8 +2606,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>136151</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2552,8 +2654,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>98053</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2601,7 +2703,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2649,7 +2751,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>187023</xdr:rowOff>
+      <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2793,7 +2895,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3142,8 +3244,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>136151</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3190,8 +3292,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>98053</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3239,7 +3341,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3287,7 +3389,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>187023</xdr:rowOff>
+      <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3431,7 +3533,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4341,79 +4443,200 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\Amazon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBDFA18-E5CE-4FF5-9346-C4944D5B64A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63439A11-3D25-4EBD-9AFB-2F4C615694CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="122">
   <si>
     <t>name</t>
   </si>
@@ -337,9 +337,6 @@
     <t>https://m.media-amazon.com/images/G/32/br-events/2026/deals/kitchen._CB784221136_UC432,290_.jpg</t>
   </si>
   <si>
-    <t>10% off em Eletrônicos</t>
-  </si>
-  <si>
     <t>https://amzn.to/4tQizbN</t>
   </si>
   <si>
@@ -359,6 +356,36 @@
   </si>
   <si>
     <t>20% off em Cozinha</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/OHL/Limpeza._CB780313367_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>20% off em Limpeza</t>
+  </si>
+  <si>
+    <t>https://amzn.to/48yNPU3</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/OHL/garrafastermicas._CB780313367_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>30% off em Garrafas Térmicas</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4cWSK2j</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/G/32/OHL/tech._CB780313367_UC432,290_.jpg</t>
+  </si>
+  <si>
+    <t>20% off em Acessórios Tech</t>
+  </si>
+  <si>
+    <t>https://amzn.to/49cRI19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10% off em Eletrônicos </t>
   </si>
 </sst>
 </file>
@@ -979,7 +1006,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187021</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1089,7 +1116,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1474,7 +1501,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187021</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1584,7 +1611,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2016,8 +2043,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>98053</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2113,7 +2140,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187021</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2209,7 +2236,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2654,8 +2681,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>98053</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2751,7 +2778,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187021</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2847,7 +2874,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3292,8 +3319,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>98053</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3389,7 +3416,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187021</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3485,7 +3512,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4543,13 +4570,13 @@
     </row>
     <row r="31" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="B31" t="s">
         <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
         <v>80</v>
@@ -4557,13 +4584,13 @@
     </row>
     <row r="32" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
         <v>80</v>
@@ -4571,13 +4598,13 @@
     </row>
     <row r="33" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B33" t="s">
         <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
         <v>80</v>
@@ -4585,26 +4612,59 @@
     </row>
     <row r="34" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
         <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
+    <row r="35" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
